--- a/templates/sendoff-aid-stations.xlsx
+++ b/templates/sendoff-aid-stations.xlsx
@@ -63,7 +63,7 @@
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
@@ -84,7 +84,7 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Arrive cutoff (hours)</t>
+          <t xml:space="preserve">Cutoff (day and time)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
@@ -222,8 +222,10 @@
       <c r="B5">
         <v>17.9</v>
       </c>
-      <c r="C5">
-        <v>5.5</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat 12:30 PM</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -260,8 +262,10 @@
       <c r="B6">
         <v>24.6</v>
       </c>
-      <c r="C6">
-        <v>8</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat 3:00 PM</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -293,8 +297,10 @@
       <c r="B7">
         <v>31.1</v>
       </c>
-      <c r="C7">
-        <v>10</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat 5:00 PM</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -366,48 +372,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrive cutoff (hours): hours from the start, like 30 or 30:00. Leave empty if there is none.</t>
+          <t xml:space="preserve">Cutoff: the day and time the race publishes, like Sun 1:00 PM, in the race's time zone.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crew can meet, Drop bag, Pacer pickup, Checkpoint only: yes or no. Empty means no,</t>
+          <t xml:space="preserve">   With no day, like 6:00 AM, it is the first 6:00 AM after the cutoff above it.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   except Crew can meet, where empty means yes.</t>
+          <t xml:space="preserve">   A number on its own, like 30, is hours from the start. Leave empty if there is none.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checkpoint only: a timing point with no aid, where the racer is logged but nobody meets them.</t>
+          <t xml:space="preserve">Crew can meet, Drop bag, Pacer pickup, Checkpoint only: yes or no. Empty means no,</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crew note: parking, walk-in, anything the crew needs to know getting there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t xml:space="preserve">   except Crew can meet, where empty means yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checkpoint only: a timing point with no aid, where the racer is logged but nobody meets them.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Crew note: parking, walk-in, anything the crew needs to know getting there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Only the first sheet is read. Columns can be in any order, and extra columns are ignored.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">Delete the example rows and put in your own, then import the file in SendOff.</t>
         </is>
